--- a/dws-pipeline-analyzer/templates/变更清单_示例.xlsx
+++ b/dws-pipeline-analyzer/templates/变更清单_示例.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表级变更" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段级变更" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变动类型说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="受影响表清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变动类型说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -168,6 +169,21 @@
 </file>
 
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>模板</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>从血缘平台整理的受影响表名列表。填表名即可（可含schema前缀，工具自动归一化）。一行一张表。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>模板</author>
@@ -1083,6 +1099,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>受影响的表名</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dwb_user_info_f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dwb_order_f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dws.dwb_trade_sum_f</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
